--- a/models/Extra/WACC_calculation/cinv_risk_free.xlsx
+++ b/models/Extra/WACC_calculation/cinv_risk_free.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\msc-thesis-incomplete-markets-LDES\models\Extra\WACC_calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855072EB-6C95-4AE1-9449-65045D05A997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68AC335-CD0A-4D74-915B-477D184117F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F02FDA62-4D99-42AF-9059-B760232356C5}"/>
   </bookViews>

--- a/models/Extra/WACC_calculation/cinv_risk_free.xlsx
+++ b/models/Extra/WACC_calculation/cinv_risk_free.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\msc-thesis-incomplete-markets-LDES\models\Extra\WACC_calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68AC335-CD0A-4D74-915B-477D184117F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7229E880-4D23-44D5-9601-D3847D6E67F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F02FDA62-4D99-42AF-9059-B760232356C5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4102" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4105" uniqueCount="81">
   <si>
     <t>WACC</t>
   </si>
@@ -274,6 +274,12 @@
   <si>
     <t xml:space="preserve">H2_E min </t>
   </si>
+  <si>
+    <t>implied WACC</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
 </sst>
 </file>
 
@@ -332,7 +338,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -340,12 +346,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -375,7 +379,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>56377</xdr:colOff>
+      <xdr:colOff>56378</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>54499</xdr:rowOff>
     </xdr:to>
@@ -810,7 +814,7 @@
     <col min="5" max="5" width="13.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" customWidth="1"/>
     <col min="10" max="10" width="17.21875" customWidth="1"/>
     <col min="11" max="11" width="16.109375" customWidth="1"/>
     <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -1200,14 +1204,14 @@
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
@@ -1498,14 +1502,14 @@
       <c r="I26" s="5"/>
     </row>
     <row r="27" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
       <c r="H27" s="5"/>
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.3">
@@ -1701,14 +1705,14 @@
       <c r="G38" s="5"/>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
@@ -2141,16 +2145,16 @@
       <c r="G50" s="5"/>
     </row>
     <row r="51" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
     </row>
     <row r="52" spans="2:13" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
@@ -2525,21 +2529,18 @@
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
     </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B65" s="7" t="s">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B65" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
     </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
         <v>24</v>
       </c>
@@ -2552,14 +2553,15 @@
       <c r="F66" t="s">
         <v>23</v>
       </c>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
+      <c r="I66" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
       <c r="L66" s="8"/>
       <c r="M66" s="8"/>
-      <c r="N66" s="8"/>
-      <c r="O66" s="8"/>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B67" s="6">
         <v>0.9</v>
       </c>
@@ -2579,6 +2581,9 @@
         <f>I41/$I$10</f>
         <v>1.1772705099861984</v>
       </c>
+      <c r="I67" t="s">
+        <v>80</v>
+      </c>
       <c r="J67" t="s">
         <v>75</v>
       </c>
@@ -2592,7 +2597,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B68" s="6">
         <v>0.8</v>
       </c>
@@ -2615,21 +2620,21 @@
       <c r="I68" s="6">
         <v>1</v>
       </c>
-      <c r="J68" s="9">
+      <c r="J68" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K68" s="9">
+      <c r="K68" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L68" s="9">
+      <c r="L68" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="M68" s="9">
+      <c r="M68" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="N68" s="9"/>
+      <c r="N68" s="7"/>
     </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B69" s="6">
         <v>0.7</v>
       </c>
@@ -2652,21 +2657,21 @@
       <c r="I69" s="6">
         <v>0.9</v>
       </c>
-      <c r="J69" s="9">
+      <c r="J69" s="7">
         <v>7.5283150103654897E-2</v>
       </c>
-      <c r="K69" s="9">
+      <c r="K69" s="7">
         <v>7.4898800000000001E-2</v>
       </c>
-      <c r="L69" s="9">
+      <c r="L69" s="7">
         <v>9.3688451983004906E-2</v>
       </c>
-      <c r="M69" s="9">
+      <c r="M69" s="7">
         <v>7.6565800000000003E-2</v>
       </c>
-      <c r="N69" s="9"/>
+      <c r="N69" s="7"/>
     </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B70" s="6">
         <v>0.6</v>
       </c>
@@ -2689,21 +2694,21 @@
       <c r="I70" s="6">
         <v>0.8</v>
       </c>
-      <c r="J70" s="9">
+      <c r="J70" s="7">
         <v>8.0876251990646297E-2</v>
       </c>
-      <c r="K70" s="9">
+      <c r="K70" s="7">
         <v>8.0485000000000001E-2</v>
       </c>
-      <c r="L70" s="9">
+      <c r="L70" s="7">
         <v>0.103466188023165</v>
       </c>
-      <c r="M70" s="9">
+      <c r="M70" s="7">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="N70" s="9"/>
+      <c r="N70" s="7"/>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B71" s="6">
         <v>0.5</v>
       </c>
@@ -2726,21 +2731,21 @@
       <c r="I71" s="6">
         <v>0.7</v>
       </c>
-      <c r="J71" s="9">
+      <c r="J71" s="7">
         <v>8.6849477849465395E-2</v>
       </c>
-      <c r="K71" s="9">
+      <c r="K71" s="7">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="L71" s="9">
+      <c r="L71" s="7">
         <v>0.113608057470119</v>
       </c>
-      <c r="M71" s="9">
-        <v>0.90978999999999999</v>
-      </c>
-      <c r="N71" s="9"/>
+      <c r="M71" s="7">
+        <v>9.0979000000000004E-2</v>
+      </c>
+      <c r="N71" s="7"/>
     </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B72" s="6">
         <v>0.4</v>
       </c>
@@ -2763,21 +2768,21 @@
       <c r="I72" s="6">
         <v>0.6</v>
       </c>
-      <c r="J72" s="9">
+      <c r="J72" s="7">
         <v>9.3246381622698493E-2</v>
       </c>
-      <c r="K72" s="9">
+      <c r="K72" s="7">
         <v>9.2799999999999994E-2</v>
       </c>
-      <c r="L72" s="9">
+      <c r="L72" s="7">
         <v>0.12461005912323</v>
       </c>
-      <c r="M72" s="9">
+      <c r="M72" s="7">
         <v>0.1132</v>
       </c>
-      <c r="N72" s="9"/>
+      <c r="N72" s="7"/>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B73" s="6">
         <v>0.3</v>
       </c>
@@ -2800,21 +2805,21 @@
       <c r="I73" s="6">
         <v>0.5</v>
       </c>
-      <c r="J73" s="9">
+      <c r="J73" s="7">
         <v>9.8089389536052202E-2</v>
       </c>
-      <c r="K73" s="9">
+      <c r="K73" s="7">
         <v>9.7689999999999999E-2</v>
       </c>
-      <c r="L73" s="9">
+      <c r="L73" s="7">
         <v>0.14188684429461301</v>
       </c>
-      <c r="M73" s="9">
+      <c r="M73" s="7">
         <v>0.12764700000000001</v>
       </c>
-      <c r="N73" s="9"/>
+      <c r="N73" s="7"/>
     </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B74" s="6">
         <v>0.2</v>
       </c>
@@ -2837,21 +2842,21 @@
       <c r="I74" s="6">
         <v>0.4</v>
       </c>
-      <c r="J74" s="9">
+      <c r="J74" s="7">
         <v>0.101571846421427</v>
       </c>
-      <c r="K74" s="9">
+      <c r="K74" s="7">
         <v>0.1011</v>
       </c>
-      <c r="L74" s="9">
+      <c r="L74" s="7">
         <v>0.16994366232111599</v>
       </c>
-      <c r="M74" s="9">
+      <c r="M74" s="7">
         <v>0.15265999999999999</v>
       </c>
-      <c r="N74" s="9"/>
+      <c r="N74" s="7"/>
     </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B75" s="6">
         <v>0.1</v>
       </c>
@@ -2874,21 +2879,21 @@
       <c r="I75" s="6">
         <v>0.3</v>
       </c>
-      <c r="J75" s="9">
+      <c r="J75" s="7">
         <v>0.10273443715569799</v>
       </c>
-      <c r="K75" s="9">
+      <c r="K75" s="7">
         <v>0.10226</v>
       </c>
-      <c r="L75" s="9">
+      <c r="L75" s="7">
         <v>0.21788121191409299</v>
       </c>
-      <c r="M75" s="9">
+      <c r="M75" s="7">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="N75" s="9"/>
+      <c r="N75" s="7"/>
     </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.3">
       <c r="C76" s="5"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
@@ -2896,21 +2901,21 @@
       <c r="I76" s="6">
         <v>0.2</v>
       </c>
-      <c r="J76" s="9">
+      <c r="J76" s="7">
         <v>9.4717651971547606E-2</v>
       </c>
-      <c r="K76" s="9">
+      <c r="K76" s="7">
         <v>9.4280000000000003E-2</v>
       </c>
-      <c r="L76" s="9">
+      <c r="L76" s="7">
         <v>0.296522892176945</v>
       </c>
-      <c r="M76" s="9">
+      <c r="M76" s="7">
         <v>0.26069999999999999</v>
       </c>
-      <c r="N76" s="9"/>
+      <c r="N76" s="7"/>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B77" s="6"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5"/>
@@ -2920,21 +2925,21 @@
       <c r="I77" s="6">
         <v>0.1</v>
       </c>
-      <c r="J77" s="9">
+      <c r="J77" s="7">
         <v>7.7626743108615198E-2</v>
       </c>
-      <c r="K77" s="9">
+      <c r="K77" s="7">
         <v>7.6950000000000005E-2</v>
       </c>
-      <c r="L77" s="9">
+      <c r="L77" s="7">
         <v>0.52414578984999705</v>
       </c>
-      <c r="M77" s="9">
+      <c r="M77" s="7">
         <v>0.15418000000000001</v>
       </c>
-      <c r="N77" s="9"/>
+      <c r="N77" s="7"/>
     </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B78" s="6"/>
       <c r="C78" s="5"/>
       <c r="D78" s="5"/>
@@ -2945,13 +2950,16 @@
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
     </row>
-    <row r="79" spans="2:15" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="6"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
+      <c r="I79" t="s">
+        <v>80</v>
+      </c>
       <c r="J79" t="s">
         <v>71</v>
       </c>
@@ -2965,7 +2973,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" spans="2:15" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="6"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5"/>
@@ -2975,16 +2983,16 @@
       <c r="I80" s="6">
         <v>1</v>
       </c>
-      <c r="J80" s="9">
+      <c r="J80" s="7">
         <v>0.06</v>
       </c>
-      <c r="K80" s="9">
+      <c r="K80" s="7">
         <v>0.06</v>
       </c>
-      <c r="L80" s="9">
+      <c r="L80" s="7">
         <v>0.06</v>
       </c>
-      <c r="M80" s="9">
+      <c r="M80" s="7">
         <v>0.06</v>
       </c>
     </row>
@@ -2998,16 +3006,16 @@
       <c r="I81" s="6">
         <v>0.9</v>
       </c>
-      <c r="J81" s="9">
+      <c r="J81" s="7">
         <v>0.06</v>
       </c>
-      <c r="K81" s="9">
+      <c r="K81" s="7">
         <v>0.06</v>
       </c>
-      <c r="L81" s="9">
+      <c r="L81" s="7">
         <v>6.1249999999999999E-2</v>
       </c>
-      <c r="M81" s="9">
+      <c r="M81" s="7">
         <v>0.06</v>
       </c>
     </row>
@@ -3021,16 +3029,16 @@
       <c r="I82" s="6">
         <v>0.8</v>
       </c>
-      <c r="J82" s="9">
+      <c r="J82" s="7">
         <v>0.06</v>
       </c>
-      <c r="K82" s="9">
+      <c r="K82" s="7">
         <v>0.06</v>
       </c>
-      <c r="L82" s="9">
+      <c r="L82" s="7">
         <v>6.5710000000000005E-2</v>
       </c>
-      <c r="M82" s="9">
+      <c r="M82" s="7">
         <v>6.2600000000000003E-2</v>
       </c>
     </row>
@@ -3044,16 +3052,16 @@
       <c r="I83" s="6">
         <v>0.7</v>
       </c>
-      <c r="J83" s="9">
+      <c r="J83" s="7">
         <v>0.06</v>
       </c>
-      <c r="K83" s="9">
+      <c r="K83" s="7">
         <v>0.06</v>
       </c>
-      <c r="L83" s="9">
+      <c r="L83" s="7">
         <v>7.0199999999999999E-2</v>
       </c>
-      <c r="M83" s="9">
+      <c r="M83" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -3067,16 +3075,16 @@
       <c r="I84" s="6">
         <v>0.6</v>
       </c>
-      <c r="J84" s="9">
+      <c r="J84" s="7">
         <v>0.06</v>
       </c>
-      <c r="K84" s="9">
+      <c r="K84" s="7">
         <v>0.06</v>
       </c>
-      <c r="L84" s="9">
+      <c r="L84" s="7">
         <v>7.8899999999999998E-2</v>
       </c>
-      <c r="M84" s="9">
+      <c r="M84" s="7">
         <v>7.2300000000000003E-2</v>
       </c>
     </row>
@@ -3090,16 +3098,16 @@
       <c r="I85" s="6">
         <v>0.5</v>
       </c>
-      <c r="J85" s="9">
+      <c r="J85" s="7">
         <v>0.06</v>
       </c>
-      <c r="K85" s="9">
+      <c r="K85" s="7">
         <v>0.06</v>
       </c>
-      <c r="L85" s="9">
+      <c r="L85" s="7">
         <v>7.9280000000000003E-2</v>
       </c>
-      <c r="M85" s="9">
+      <c r="M85" s="7">
         <v>7.4800000000000005E-2</v>
       </c>
     </row>
@@ -3113,16 +3121,16 @@
       <c r="I86" s="6">
         <v>0.4</v>
       </c>
-      <c r="J86" s="9">
+      <c r="J86" s="7">
         <v>0.06</v>
       </c>
-      <c r="K86" s="9">
+      <c r="K86" s="7">
         <v>0.06</v>
       </c>
-      <c r="L86" s="9">
+      <c r="L86" s="7">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="M86" s="9">
+      <c r="M86" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -3136,16 +3144,16 @@
       <c r="I87" s="6">
         <v>0.3</v>
       </c>
-      <c r="J87" s="9">
+      <c r="J87" s="7">
         <v>0.06</v>
       </c>
-      <c r="K87" s="9">
+      <c r="K87" s="7">
         <v>0.06</v>
       </c>
-      <c r="L87" s="9">
+      <c r="L87" s="7">
         <v>8.8190000000000004E-2</v>
       </c>
-      <c r="M87" s="9">
+      <c r="M87" s="7">
         <v>0.06</v>
       </c>
     </row>
@@ -3159,16 +3167,16 @@
       <c r="I88" s="6">
         <v>0.2</v>
       </c>
-      <c r="J88" s="9">
+      <c r="J88" s="7">
         <v>0.06</v>
       </c>
-      <c r="K88" s="9">
+      <c r="K88" s="7">
         <v>0.06</v>
       </c>
-      <c r="L88" s="9">
+      <c r="L88" s="7">
         <v>9.6750000000000003E-2</v>
       </c>
-      <c r="M88" s="9">
+      <c r="M88" s="7">
         <v>8.7790000000000007E-2</v>
       </c>
     </row>
@@ -3182,17 +3190,17 @@
       <c r="I89" s="6">
         <v>0.1</v>
       </c>
-      <c r="J89" s="9">
+      <c r="J89" s="7">
         <v>0.10352472177457001</v>
       </c>
-      <c r="K89" s="9">
+      <c r="K89" s="7">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="L89" s="9">
+      <c r="L89" s="7">
         <v>0.117737416875713</v>
       </c>
-      <c r="M89" s="9">
-        <v>6.0000000000000001E-3</v>
+      <c r="M89" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
@@ -56351,7 +56359,8 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C223:D237">
     <sortCondition ref="D223:D237"/>
   </sortState>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="I66:M66"/>
     <mergeCell ref="B51:I51"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B27:G27"/>
